--- a/report/naloga1.xlsx
+++ b/report/naloga1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tilen\github\magisterij\first_homework_cs\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tilen\github\magisterij\rs-homework-1\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F66554BD-0F6B-4681-B7A5-D870962ECED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1F3FB7-DE72-476A-B48E-45FFE16C7D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{87077ABD-8CC0-457E-A7D5-A537ECDD9400}"/>
+    <workbookView xWindow="1440" yWindow="1440" windowWidth="16200" windowHeight="9307" activeTab="3" xr2:uid="{87077ABD-8CC0-457E-A7D5-A537ECDD9400}"/>
   </bookViews>
   <sheets>
     <sheet name="Naloga1a" sheetId="1" r:id="rId1"/>
@@ -18,23 +18,6 @@
     <sheet name="Naloga1c" sheetId="2" r:id="rId3"/>
     <sheet name="Naloga1d" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Naloga1d!$A$3</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Naloga1d!$A$8</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Naloga1d!$A$3</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Naloga1d!$A$8</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Naloga1d!$B$3:$D$3</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Naloga1d!$B$6:$D$6</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Naloga1d!$B$8:$D$8</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Naloga1d!$B$3:$D$3</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Naloga1d!$B$6:$D$6</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Naloga1d!$B$8:$D$8</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Naloga1d!$A$3</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Naloga1d!$A$8</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Naloga1d!$B$3:$D$3</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Naloga1d!$B$6:$D$6</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Naloga1d!$B$8:$D$8</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -99,7 +82,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -182,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -199,12 +182,11 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -358,19 +340,19 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.55937700000000001</c:v>
+                  <c:v>0.84409199999999995</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.61643000000000003</c:v>
+                  <c:v>1.0089520000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.63878500000000005</c:v>
+                  <c:v>1.138954</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.64649000000000001</c:v>
+                  <c:v>1.144836</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.64649000000000001</c:v>
+                  <c:v>1.144836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -450,8 +432,7 @@
         <c:axId val="1184068896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="0.66000000000000014"/>
-          <c:min val="0.55000000000000004"/>
+          <c:min val="0.8"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -695,13 +676,13 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.64649000000000001</c:v>
+                  <c:v>1.144836</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69483399999999995</c:v>
+                  <c:v>1.192469</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.72430000000000005</c:v>
+                  <c:v>1.2103189999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -773,16 +754,16 @@
             <c:numRef>
               <c:f>Naloga1c!$B$6:$D$6</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.61432900000000001</c:v>
+                  <c:v>1.3868039999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.68737999999999999</c:v>
+                  <c:v>1.5122979999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.74304999999999999</c:v>
+                  <c:v>1.643418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -862,8 +843,7 @@
         <c:axId val="1184108256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="0.75000000000000011"/>
-          <c:min val="0.60000000000000009"/>
+          <c:min val="1.1000000000000001"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1128,16 +1108,16 @@
             <c:numRef>
               <c:f>Naloga1d!$B$2:$D$2</c:f>
               <c:numCache>
-                <c:formatCode>0.000000</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.64804099999999998</c:v>
+                <c:pt idx="0" formatCode="0.000000">
+                  <c:v>1.142725</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.67316299999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.67102700000000004</c:v>
+                  <c:v>1.2720880000000001</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.000000">
+                  <c:v>1.255768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1209,16 +1189,16 @@
             <c:numRef>
               <c:f>Naloga1d!$B$7:$D$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.61511300000000002</c:v>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>1.3766080000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.64463300000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63963800000000004</c:v>
+                  <c:v>1.6145400000000001</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>1.5933090000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1447,27 +1427,13 @@
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-              <a:lnSpc>
-                <a:spcPct val="100000"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buClrTx/>
-              <a:buSzTx/>
-              <a:buFontTx/>
-              <a:buNone/>
-              <a:tabLst/>
+            <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
+                  <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
-                  </a:sysClr>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1475,17 +1441,9 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="sl-SI" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="sl-SI"/>
               <a:t>Vpliv števila fizičnih registrov na število zastojev</a:t>
             </a:r>
-            <a:endParaRPr lang="sl-SI"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1501,27 +1459,13 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
+          <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
+                <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
-                </a:sysClr>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1562,19 +1506,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
@@ -1601,10 +1533,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>8360</c:v>
+                  <c:v>7503</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4407</c:v>
+                  <c:v>4191</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1643,19 +1575,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
@@ -1682,13 +1602,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3566</c:v>
+                  <c:v>2767</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>432</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1708,7 +1628,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1263531392"/>
         <c:axId val="1263419552"/>
@@ -3613,7 +3532,7 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3721,6 +3640,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3731,6 +3655,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3762,6 +3691,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4160,16 +4092,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>264318</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>383380</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>302418</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>421480</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4202,15 +4134,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>583405</xdr:colOff>
+      <xdr:colOff>284364</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>122717</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>621505</xdr:colOff>
+      <xdr:colOff>322464</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>151292</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4612,33 +4544,33 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="9">
-        <v>2.1153620000000002</v>
-      </c>
-      <c r="C2" s="9">
-        <v>1.28342</v>
+      <c r="B2" s="8">
+        <v>1.5119990000000001</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.90045299999999995</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="8">
-        <v>173887</v>
-      </c>
-      <c r="C3" s="8">
-        <v>105501</v>
+      <c r="B3" s="7">
+        <v>101127</v>
+      </c>
+      <c r="C3" s="7">
+        <v>60225</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="9">
-        <v>0.47273199999999999</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0.77916799999999997</v>
+      <c r="B4" s="8">
+        <v>0.66137599999999996</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.110552</v>
       </c>
     </row>
   </sheetData>
@@ -4650,6 +4582,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76AA283-61A7-4533-A261-1AC05AE20148}">
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
@@ -4675,20 +4610,20 @@
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="9">
-        <v>0.55937700000000001</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.61643000000000003</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.63878500000000005</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.64649000000000001</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.64649000000000001</v>
+      <c r="B2" s="8">
+        <v>0.84409199999999995</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1.0089520000000001</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1.138954</v>
+      </c>
+      <c r="E2" s="8">
+        <v>1.144836</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1.144836</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -4736,14 +4671,14 @@
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="9">
-        <v>0.64649000000000001</v>
-      </c>
-      <c r="C2" s="10">
-        <v>0.69483399999999995</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.72430000000000005</v>
+      <c r="B2" s="8">
+        <v>1.144836</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1.192469</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1.2103189999999999</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -4770,14 +4705,14 @@
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="7">
-        <v>0.61432900000000001</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.68737999999999999</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0.74304999999999999</v>
+      <c r="B6" s="8">
+        <v>1.3868039999999999</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1.5122979999999999</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1.643418</v>
       </c>
     </row>
   </sheetData>
@@ -4813,14 +4748,14 @@
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="11">
-        <v>0.64804099999999998</v>
-      </c>
-      <c r="C2" s="11">
-        <v>0.67316299999999996</v>
-      </c>
-      <c r="D2" s="11">
-        <v>0.67102700000000004</v>
+      <c r="B2" s="10">
+        <v>1.142725</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1.2720880000000001</v>
+      </c>
+      <c r="D2" s="10">
+        <v>1.255768</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -4828,10 +4763,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="6">
-        <v>8360</v>
-      </c>
-      <c r="C3" s="6">
-        <v>4407</v>
+        <v>7503</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4191</v>
       </c>
       <c r="D3" s="6">
         <v>0</v>
@@ -4854,18 +4789,18 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="6">
-        <v>0.61511300000000002</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.64463300000000001</v>
+        <v>1.3766080000000001</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1.6145400000000001</v>
       </c>
       <c r="D7" s="6">
-        <v>0.63963800000000004</v>
+        <v>1.5933090000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
@@ -4873,13 +4808,13 @@
         <v>11</v>
       </c>
       <c r="B8" s="6">
-        <v>3566</v>
+        <v>2767</v>
       </c>
       <c r="C8" s="6">
-        <v>432</v>
+        <v>44</v>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
